--- a/Evershop_search_testing/Q2 & Q3 (Test-Cases and Execution) .xlsx
+++ b/Evershop_search_testing/Q2 & Q3 (Test-Cases and Execution) .xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Manual_Testing\Evershop_search_testing\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74FE1B4-CE58-4884-9FF9-6470A2232A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -94,15 +103,16 @@
   </si>
   <si>
     <r>
-      <rPr/>
       <t xml:space="preserve">
 Auto-suggestion not appearing for partial keyword search
 URL: </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
       </rPr>
       <t>https://demo.evershop.io/</t>
     </r>
@@ -292,106 +302,122 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -581,59 +607,62 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A3:Z16"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="16.38"/>
-    <col customWidth="1" min="4" max="4" width="44.38"/>
-    <col customWidth="1" min="5" max="5" width="29.5"/>
-    <col customWidth="1" min="6" max="6" width="29.0"/>
-    <col customWidth="1" min="7" max="7" width="32.88"/>
-    <col customWidth="1" min="8" max="8" width="36.38"/>
-    <col customWidth="1" min="9" max="9" width="19.0"/>
-    <col customWidth="1" min="10" max="10" width="7.88"/>
-    <col customWidth="1" min="11" max="11" width="28.0"/>
-    <col customWidth="1" min="12" max="12" width="22.88"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="44.33203125" customWidth="1"/>
+    <col min="5" max="5" width="29.44140625" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="32.88671875" customWidth="1"/>
+    <col min="8" max="8" width="36.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="22.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3">
+    <row r="3" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="10" t="s">
         <v>7</v>
       </c>
       <c r="J3" s="1"/>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="1"/>
@@ -651,7 +680,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -663,7 +692,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="3"/>
+      <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -679,30 +708,30 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="1"/>
@@ -723,37 +752,37 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="M6" s="1"/>
@@ -771,30 +800,30 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J7" s="1"/>
@@ -815,30 +844,30 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J8" s="1"/>
@@ -859,30 +888,30 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="1"/>
@@ -903,30 +932,30 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="1"/>
@@ -947,30 +976,30 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" ht="50.25" customHeight="1">
+    <row r="11" spans="1:26" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="1"/>
@@ -991,35 +1020,35 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="8" t="s">
         <v>64</v>
       </c>
       <c r="M12" s="1"/>
@@ -1037,39 +1066,39 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" ht="57.0" customHeight="1">
+    <row r="13" spans="1:26" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="3" t="s">
+      <c r="L13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M13" s="4">
-        <v>10.0</v>
+      <c r="M13" s="2">
+        <v>10</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1085,39 +1114,39 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" ht="27.0" customHeight="1">
+    <row r="14" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="3" t="s">
+      <c r="L14" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M14" s="4">
-        <v>9.0</v>
+      <c r="M14" s="2">
+        <v>9</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1133,27 +1162,27 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15">
-      <c r="L15" s="9" t="s">
+    <row r="15" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="L15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="8">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="L16" s="9" t="s">
+      <c r="M15" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="L16" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="M16" s="11">
+      <c r="M16" s="9">
         <v>0.9</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="K6"/>
-    <hyperlink r:id="rId2" ref="L6"/>
+    <hyperlink ref="K6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
-  <drawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>